--- a/Data/nigeria_english_nounsandPronounsfill.xlsx
+++ b/Data/nigeria_english_nounsandPronounsfill.xlsx
@@ -472,1256 +472,1256 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>155</v>
+        <v>43</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>All her ______ was stolen during the journey.</t>
+          <t>The little boy introduced ______ to the visitors.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>baggages</t>
+          <t>him</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>luggages</t>
+          <t>himself</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>luggage</t>
+          <t>his</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>suitcases</t>
+          <t>he</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>luggage</t>
+          <t>himself</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Luggage is uncountable</t>
+          <t>Reflexive pronoun is used when subject and object are the same</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>He bought two ______ of scissors for the tailoring shop.</t>
+          <t>She could not hide her ______ when she saw the gift.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pair</t>
+          <t>excite</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>pairs</t>
+          <t>excited</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>pieces</t>
+          <t>excitement</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>sets</t>
+          <t>exciting</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>pairs</t>
+          <t>excitement</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Scissors are counted in pairs</t>
+          <t>Excitement is an abstract noun</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The judge commended the witness for her ______.</t>
+          <t>Everyone must submit ______ assignment before Friday.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>brave</t>
+          <t>his</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>bravery</t>
+          <t>her</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>bravely</t>
+          <t>their</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>braves</t>
+          <t>its</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>bravery</t>
+          <t>their</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bravery is an abstract noun</t>
+          <t>Their is used as a gender-neutral pronoun</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>175</v>
+        <v>71</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The two brothers blamed ______ for the failure of the project.</t>
+          <t>The manager distributed the gifts among ______ of the workers.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>every</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>each</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>one another</t>
+          <t>all</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>any</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>each</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Used for two persons</t>
+          <t>Each refers to individuals within a group</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The teacher told the boys to share the food between ______.</t>
+          <t>The committee has postponed ______ meeting indefinitely.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>its</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>his</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>one another</t>
+          <t>her</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>its</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Them is acceptable with between</t>
+          <t>Committee used as a single unit</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The committee has submitted ______ report to the minister.</t>
+          <t>Everyone should carry ______ bag properly.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>his</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>her</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>their</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>its</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>his</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>her</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>their</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Collective noun used as a unit takes its</t>
+          <t>Their is used as a gender-neutral pronoun</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>One of the girls lost ______ purse on her way to school.</t>
+          <t>We admired the athlete’s ______ during the race.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>strength</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>hers</t>
+          <t>strongly</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>strengthen</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>strength</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>One of is singular, so her is correct</t>
+          <t>Strength is an abstract noun</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>174</v>
+        <v>107</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The committee postponed ______ decision until further notice.</t>
+          <t>The man bought three ______ of scissors from the shop.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>pair</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>pairs</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>pieces</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>sets</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>pairs</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Collective noun as a unit</t>
+          <t>Scissors are counted in pairs</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The blind deserve ______ care and attention.</t>
+          <t>The clergy ______ invited to the conference last week.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>was</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>has been</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>were</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>is</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>were</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>The blind is treated as plural</t>
+          <t>Clergy is an invariable plural noun</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The old man lost all his ______ during the flood.</t>
+          <t>The principal demanded an explanation for the students’ ______.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>property</t>
+          <t>behave</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>properties</t>
+          <t>behaved</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>belonging</t>
+          <t>behavior</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>belongings</t>
+          <t>behaving</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>belongings</t>
+          <t>behavior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Belongings is a plural-only noun meaning personal possessions</t>
+          <t>Behavior is the correct noun form</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The news about the election ______ encouraging.</t>
+          <t>Neither of the two boys remembered ______ locker number.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>his</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>hers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>its</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>his</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>News is grammatically singular</t>
+          <t>Neither is singular</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The doctor advised the patient to take ______ medicine regularly.</t>
+          <t>All her ______ was stolen at the motor park.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>luggages</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>herself</t>
+          <t>luggage</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>hers</t>
+          <t>baggages</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>she</t>
+          <t>suitcase</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>luggage</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Reflexive pronoun was chosen</t>
+          <t>Luggage is uncountable</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The principal and the vice-principal blamed ______ for the poor performance of the school.</t>
+          <t>She could not hide her ______ when she heard the news.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>sadness</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>one another</t>
+          <t>sadly</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>saddens</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>sadness</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>They blamed themselves, not each other</t>
+          <t>Sadness is the abstract noun form of sad</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The teacher asked the pupils to keep their ______ tidy.</t>
+          <t>Either John or his brothers will bring ______ books to school.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>hair</t>
+          <t>his</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>hairs</t>
+          <t>their</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>hair’s</t>
+          <t>his or her</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>hairses</t>
+          <t>its</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>hair</t>
+          <t>their</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hair is uncountable when referring to all hair</t>
+          <t>Pronoun agrees with the nearer subject</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>He bought three ______ of trousers at the market.</t>
+          <t>One of the boys forgot ______ textbook at home.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>pair</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>pairs</t>
+          <t>his</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>pieces</t>
+          <t>her</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>sets</t>
+          <t>its</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>pairs</t>
+          <t>his</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Trousers are counted in pairs</t>
+          <t>Headword one is singular</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>One of the boys forgot ______ bag in the classroom.</t>
+          <t>This is the man ______ house was destroyed by fire.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>who</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>whom</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>whose</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>which</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>whose</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>One of is singular, so his is correct</t>
+          <t>Whose shows possession</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The poor old man had lost all his ______ in the fire.</t>
+          <t>The girl blamed ______ for the mistake she made.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>property</t>
+          <t>her</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>properties</t>
+          <t>herself</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>belonging</t>
+          <t>hers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>belongings</t>
+          <t>she</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>belongings</t>
+          <t>herself</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Belongings is a plural-only noun meaning personal possessions</t>
+          <t>Reflexive pronoun is required</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>50</v>
+        <v>162</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The manager rewarded the workers for their ______.</t>
+          <t>All the stolen goods were recovered, but none of the ______ was returned to the owner.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>honest</t>
+          <t>belongings</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>honesty</t>
+          <t>properties</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>honestly</t>
+          <t>furnitures</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>honesties</t>
+          <t>luggage</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>honesty</t>
+          <t>luggage</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Honesty is an abstract noun</t>
+          <t>Luggage is uncountable</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>He gave me some useful ______ before I travelled.</t>
+          <t>The baby cried because it had lost ______ toy.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>advices</t>
+          <t>it</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>advice</t>
+          <t>its</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>advisory</t>
+          <t>itself</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>advise</t>
+          <t>it’s</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>advice</t>
+          <t>its</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Advice is uncountable</t>
+          <t>Its is the possessive form of it</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The man ______ daughter won the scholarship is my uncle.</t>
+          <t>The teacher asked us to mind ______ language in public.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>who</t>
+          <t>our</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>whom</t>
+          <t>us</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>whose</t>
+          <t>ourselves</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>which</t>
+          <t>we</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>whose</t>
+          <t>our</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Whose shows possession</t>
+          <t>Possessive adjective is required</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The furniture in the room ______ very expensive.</t>
+          <t>The thief escaped with all the stolen ______.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>furniture</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>furnitures</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>furnishing</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>furnished</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>furniture</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Furniture is uncountable and singular</t>
+          <t>Furniture is an uncountable noun</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Either of the girls forgot ______ handbag in the classroom.</t>
+          <t>One should always mind ______ language when addressing elders.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>his</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>her</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>their</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>her</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>hers</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>one’s</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>one’s</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Either is singular</t>
+          <t>Pronoun agrees with one</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124</v>
+        <v>57</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Neither of the boys admitted ______ mistake.</t>
+          <t>The old man lost all his ______ in the robbery.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>property</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>properties</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>hers</t>
+          <t>belonging</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>belongings</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>belongings</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Neither is singular</t>
+          <t>Belongings is a plural-only noun</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The committee postponed ______ decision till next week.</t>
+          <t>He bought two ______ trousers from the market.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>pair</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>pairs of</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>pieces of</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>sets of</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>pairs of</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Committee as a unit is singular</t>
+          <t>Correct quantity expression</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The crowd expressed their ______ at the referee’s controversial decision.</t>
+          <t>One of the girls forgot ______ purse in the hall.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>disapprove</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>disapproving</t>
+          <t>her</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>disapproval</t>
+          <t>hers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>disapproved</t>
+          <t>its</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>disapproval</t>
+          <t>her</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Disapproval is the correct noun</t>
+          <t>Headword one is singular</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The success of the project was due to their hard ______.</t>
+          <t>The passers-by ______ shocked by the explosion.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>work</t>
+          <t>was</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>works</t>
+          <t>were</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>worked</t>
+          <t>has been</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>is</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>work</t>
+          <t>were</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Work is uncountable here</t>
+          <t>Passers-by is plural</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>30</v>
+        <v>170</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The woman congratulated ______ on her success.</t>
+          <t>The principal and the secretary congratulated ______ on the success of the programme.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>herself</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>hers</t>
+          <t>one another</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>she</t>
+          <t>them</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>herself</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Reflexive pronoun is required</t>
+          <t>Exactly two people</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The police ______ arrived late at the scene of the accident.</t>
+          <t>The accused pleaded guilty to ______ crimes.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>has</t>
+          <t>his</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>was</t>
+          <t>their</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>her</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>its</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>their</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Police is always plural</t>
+          <t>Accused refers to more than one person</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>156</v>
+        <v>85</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The jury ______ divided in their opinion.</t>
+          <t>The rich always ______ for better living conditions.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>was</t>
+          <t>struggle</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>has been</t>
+          <t>struggles</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>struggling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>struggled</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>struggle</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Division shows plural sense</t>
+          <t>The rich is plural and takes a plural verb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The dog wagged ______ tail excitedly.</t>
+          <t>The company’s headquarters ______ located in Lagos.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>are</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>were</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>itself</t>
+          <t>is</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>it’s</t>
+          <t>have</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>are</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Its is the possessive form of it</t>
+          <t>Headquarters is an invariable plural noun</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The boy and his sister blamed ______ for the broken plate.</t>
+          <t>The girl was punished for ______ during the examination.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>cheat</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>one another</t>
+          <t>cheating</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>cheated</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>cheats</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>cheating</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>They blamed themselves</t>
+          <t>Gerund follows the preposition for</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The boy looked at ______ in the mirror and smiled.</t>
+          <t>Either of the boys forgot ______ school bag.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>him</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1731,324 +1731,324 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>himself</t>
+          <t>hers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>he</t>
+          <t>its</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>himself</t>
+          <t>his</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Reflexive pronoun is required</t>
+          <t>Either is singular</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>20</v>
+        <v>154</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The bag on the chair is not mine; it is ______.</t>
+          <t>The boy, together with his friends, forgot ______ identity card.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>his</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>hers</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>she</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>herself</t>
+          <t>its</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>hers</t>
+          <t>his</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Hers is a possessive pronoun used independently</t>
+          <t>Main subject is singular</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The cattle ______ crossing the road when the accident occurred.</t>
+          <t>The furniture in the showroom were sold, but the ______ in the store remain.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>one</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>was</t>
+          <t>ones</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>them</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>has</t>
+          <t>theirs</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>ones</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Cattle is plural</t>
+          <t>Ones replaces previously mentioned plural items</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>He has lost all his ______ in the business venture.</t>
+          <t>The ______ of cattle was seen grazing near the river.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>saving</t>
+          <t>herd</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>savings</t>
+          <t>group</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>save</t>
+          <t>bunch</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>savers</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>savings</t>
+          <t>herd</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Savings is a plural-only noun</t>
+          <t>Herd is the correct collective noun for cattle</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>163</v>
+        <v>121</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The man, as well as his children, forgot ______ identity cards at home.</t>
+          <t>The ______ of the trousers he ordered online were too tight.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>pair</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>pairs</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>hers</t>
+          <t>piece</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>pieces</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>pairs</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Main subject controls the pronoun</t>
+          <t>Plural verb requires the plural headword pairs</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>He packed all his ______ into a small suitcase.</t>
+          <t>The accused, together with his accomplices, denied ______ guilt.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>cloth</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>clothes</t>
+          <t>his</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>clothe</t>
+          <t>her</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>clothing</t>
+          <t>its</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>clothes</t>
+          <t>his</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Clothes is a plural noun for garments</t>
+          <t>The main subject determines the pronoun</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The thieves escaped with all the stolen ______.</t>
+          <t>The committee congratulated ______ on a job well done.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>it</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>its</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>goodness</t>
+          <t>itself</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>goody</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>itself</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Goods means property or items</t>
+          <t>Committee is treated as a single unit</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The audience showed ______ displeasure by booing loudly.</t>
+          <t>The rich ______ not always contented with what they have.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>is</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>was</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>are</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>has</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>are</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Audience treated as a unit</t>
+          <t>The rich refers to people and is plural</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The jury finally gave ______ verdict after two hours.</t>
+          <t>The audience showed ______ appreciation with loud applause.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>its</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>their</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>its</t>
-        </is>
-      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>his</t>
@@ -2061,1022 +2061,1022 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>their</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Collective noun acting as a unit takes its</t>
+          <t>Audience is treated as plural here</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The committee has postponed ______ decision till next week.</t>
+          <t>The jury finally gave ______ verdict after long deliberation.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>its</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>their</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>his</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>her</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>its</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>their</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>themselves</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>its</t>
-        </is>
-      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Committee is treated as singular here</t>
+          <t>Jury treated as a unit here</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The principal and the vice-principal shared ______ office.</t>
+          <t>The chairman and his secretary congratulated ______ on the success of the programme.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>one another</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>them</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Two people require a plural possessive</t>
+          <t>They congratulated themselves</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The crowd expressed their ______ at the sudden announcement.</t>
+          <t>She has a deep ______ of modern literature.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>surprise</t>
+          <t>know</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>surprised</t>
+          <t>knowing</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>surprising</t>
+          <t>knowledge</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>surprisingly</t>
+          <t>knowledgeable</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>surprise</t>
+          <t>knowledge</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Surprise is the correct noun</t>
+          <t>Knowledge is the correct noun form</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>151</v>
+        <v>14</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The audience ______ applauding loudly at the end of the play.</t>
+          <t>The boys enjoyed ______ during the excursion.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>was</t>
+          <t>them</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>has been</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>their</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>theirs</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>was</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Audience viewed as one body</t>
+          <t>Reflexive pronoun is used</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The poor woman earned her living by selling ______.</t>
+          <t>The accused, together with his lawyers, denied ______ involvement.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>cloth</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>clothes</t>
+          <t>his</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>clothing</t>
+          <t>her</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>cloths</t>
+          <t>its</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>clothing</t>
+          <t>his</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Clothing is an uncountable noun</t>
+          <t>Main subject determines the pronoun</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The cattle ______ grazing behind the school.</t>
+          <t>This is one of the problems for which there is no easy ______.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>solve</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>was</t>
+          <t>solver</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>solution</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>has</t>
+          <t>solving</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>solution</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Cattle is an invariable plural noun</t>
+          <t>Solution is the correct noun form</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The police ______ the stolen car yesterday.</t>
+          <t>My elder brother bought two ______ for the new house.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>recovers</t>
+          <t>dining tables</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>has recovered</t>
+          <t>dining-tables</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>were recovering</t>
+          <t>dinings table</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>recovered</t>
+          <t>dining table</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>recovered</t>
+          <t>dining tables</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Yesterday requires simple past</t>
+          <t>Dining table forms its plural normally</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>167</v>
+        <v>32</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The teacher advised the students to mind ______ business.</t>
+          <t>The teacher advised the class to mind their ______.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>manner</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>manners</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>hers</t>
+          <t>mannings</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>mannerism</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>manners</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Students is plural</t>
+          <t>The idiom is mind your manners</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The police have recovered all the missing ______.</t>
+          <t>This is the child ______ father is a renowned doctor.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>equipment</t>
+          <t>who</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>equipments</t>
+          <t>whom</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>equip</t>
+          <t>whose</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>equipping</t>
+          <t>which</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>equipment</t>
+          <t>whose</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Equipment is uncountable</t>
+          <t>Whose expresses possession</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The poor man lived on little ______ he earned from farming.</t>
+          <t>The boys shared the food among ______.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>earning</t>
+          <t>them</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>earnings</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>earn</t>
+          <t>their</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>earns</t>
+          <t>theirs</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>earnings</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Earnings is a plural-only noun meaning income</t>
+          <t>Among themselves is correct usage</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>39</v>
+        <v>138</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The teacher punished John and ______ for the noise.</t>
+          <t>My brother bought two dining ______ for the new house.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>table</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>me</t>
+          <t>tables</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>myself</t>
+          <t>tableses</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>mine</t>
+          <t>table’s</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>me</t>
+          <t>tables</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Me is the correct object pronoun</t>
+          <t>Regular plural of table</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The woman looked at ______ in the mirror and smiled.</t>
+          <t>Neither of the twins could recognize ______ in the photograph.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>herself</t>
+          <t>one another</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>hers</t>
+          <t>himself</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>she</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>herself</t>
+          <t>himself</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Reflexive pronoun refers back to the subject</t>
+          <t>Neither is singular, so a singular reflexive pronoun is used</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The police ______ the suspects last night.</t>
+          <t>The news ______ not as good as we expected.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>arrests</t>
+          <t>are</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>has arrested</t>
+          <t>were</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>were arresting</t>
+          <t>is</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>arrested</t>
+          <t>have</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>arrested</t>
+          <t>is</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Police is plural; simple past fits</t>
+          <t>News is grammatically singular</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>157</v>
+        <v>49</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>My brother-in-law bought two new ______ yesterday.</t>
+          <t>The boys helped ______ to the remaining food.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>brother-in-laws</t>
+          <t>them</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>brothers-in-law</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>brother ins-law</t>
+          <t>their</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>brothers in laws</t>
+          <t>theirs</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>brothers-in-law</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Plural is formed on the main noun</t>
+          <t>Helped themselves is correct usage</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The players enjoyed ______ during the holiday.</t>
+          <t>The child showed remarkable ______ in solving the puzzle.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>intelligent</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>intelligence</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>intelligently</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>theirs</t>
+          <t>intelligences</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>intelligence</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Reflexive pronoun is required</t>
+          <t>Intelligence is the correct noun</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The thief stole all her ______ and disappeared.</t>
+          <t>The manager and his assistant shared the office between ______.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jewel</t>
+          <t>them</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jewellery</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>jeweller</t>
+          <t>their</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>jewelries</t>
+          <t>theirs</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>jewellery</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Jewellery is an uncountable noun</t>
+          <t>Reflexive pronoun is used for mutual action</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>He has not the ______ to face the consequences of his actions.</t>
+          <t>He has a good knowledge of African ______.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>courage</t>
+          <t>culture</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>courageous</t>
+          <t>cultures</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>courageously</t>
+          <t>cultured</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>courages</t>
+          <t>cultural</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>courage</t>
+          <t>culture</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Courage is an uncountable abstract noun</t>
+          <t>Culture is uncountable in a general sense</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The rich always ______ for better living conditions.</t>
+          <t>He has little ______ for those who break the law.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>struggle</t>
+          <t>sympathies</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>struggles</t>
+          <t>sympathy</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>struggling</t>
+          <t>sympathetic</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>struggled</t>
+          <t>sympathize</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>struggle</t>
+          <t>sympathy</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>The rich is plural</t>
+          <t>Uncountable noun</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The team has lost ______ first match of the season.</t>
+          <t>The police ______ arrived late at the scene of the robbery.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>has</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>was</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>were</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>is</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>were</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Team as a unit is singular</t>
+          <t>Police is an invariable plural noun</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The man bought two ______ of bread from the bakery.</t>
+          <t>The girl hurt ______ while playing in the rain.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>loaves</t>
+          <t>her</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>loafs</t>
+          <t>herself</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>leafs</t>
+          <t>hers</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>leaves</t>
+          <t>she</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>loaves</t>
+          <t>herself</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Plural of loaf is loaves</t>
+          <t>Reflexive pronoun refers back to the subject</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The ______ of scissors on the table belongs to the tailor.</t>
+          <t>The teacher warned the pupils not to disturb ______ during the examination.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>pair</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>pairs</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>pieces</t>
+          <t>one another</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>them</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>pair</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>We say a pair of scissors</t>
+          <t>Reciprocal action</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The jury returned to their seats and gave ______ verdict.</t>
+          <t>The boy and his sister blamed ______ for the mistake.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>one another</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>them</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Jury is treated as a plural collective noun here</t>
+          <t>Each other is used for two people</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The poor always ______ neglected by the society.</t>
+          <t>The police recovered all the stolen ______ from the warehouse.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>furniture</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>was</t>
+          <t>furnitures</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>furniture’s</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>has</t>
+          <t>furnitures’</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>furniture</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>The poor is treated as plural</t>
+          <t>Furniture is uncountable</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The children showed great ______ when their school won the competition.</t>
+          <t>Several ______ stopped to watch the accident.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>passer-by</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>happiness</t>
+          <t>passers-by</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>happily</t>
+          <t>passer-bys</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>happier</t>
+          <t>passers-bys</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>happiness</t>
+          <t>passers-by</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Happiness is the abstract noun form of happy</t>
+          <t>Plural is formed on the main noun</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The thief was arrested with all the stolen ______.</t>
+          <t>We were surprised at the boy’s display of great ______.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>courageous</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>courage</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>goodness</t>
+          <t>courageously</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>goody</t>
+          <t>courages</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>courage</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Goods refers to items or property</t>
+          <t>Courage is an abstract noun</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The teacher asked the pupils to share the sweets between ______.</t>
+          <t>Hardly had the boys finished eating when they helped ______ to the remaining food.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3106,177 +3106,177 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Between themselves is acceptable for group sharing</t>
+          <t>Helped themselves is correct reflexive usage</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>She bought two ______ of shoes for the trip.</t>
+          <t>The principal, not the teachers, gave ______ approval for the trip.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>pair</t>
+          <t>his</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>pairs</t>
+          <t>their</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>pairing</t>
+          <t>her</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>paired</t>
+          <t>its</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>pairs</t>
+          <t>his</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Pairs is the correct plural noun</t>
+          <t>Pronoun agrees with the nearer subject</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>150</v>
+        <v>98</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The man and his wife blamed ______ for the accident.</t>
+          <t>The teacher told the pupils to share the books between ______.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
+          <t>them</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>themselves</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>each other</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>one another</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>themselves</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>them</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>themselves</t>
-        </is>
-      </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>They blamed themselves</t>
+          <t>Between takes an object pronoun</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>He spent all his ______ on unnecessary luxuries.</t>
+          <t>The judge praised the witness for her ______.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>money</t>
+          <t>honest</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>monies</t>
+          <t>honestly</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>moneys</t>
+          <t>honesty</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>wealths</t>
+          <t>honesties</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>money</t>
+          <t>honesty</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Money is an uncountable noun</t>
+          <t>Honesty is an abstract noun</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>She showed great ______ in handling the difficult situation.</t>
+          <t>All her ______ was stolen at the bus stop.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>baggages</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>patiently</t>
+          <t>luggage</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>patience</t>
+          <t>suitcases</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>patients</t>
+          <t>bags</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>patience</t>
+          <t>luggage</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Patience is an abstract noun</t>
+          <t>Luggage is uncountable</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The bread she bought yesterday ______ already gone bad.</t>
+          <t>The furniture in the new office ______ very expensive.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3306,354 +3306,354 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Bread is uncountable</t>
+          <t>Furniture is uncountable and singular</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>176</v>
+        <v>60</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The furniture in the office belongs to one of the ______.</t>
+          <t>The students expressed their ______ about the new policy.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>manager</t>
+          <t>opinion</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>managers</t>
+          <t>opinions</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>manager’s</t>
+          <t>opine</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>managers’</t>
+          <t>opinionated</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>managers’</t>
+          <t>opinions</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Plural possessive is required</t>
+          <t>Opinions is the correct plural noun</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Either of the answers ______ correct.</t>
+          <t>The committee has submitted ______ report to the minister.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>its</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>his</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>her</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>its</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Either is singular</t>
+          <t>Committee as a unit takes a singular pronoun</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>She is the girl ______ name was mentioned in the report.</t>
+          <t>The news ______ too good to be true.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>who</t>
+          <t>are</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>whom</t>
+          <t>were</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>whose</t>
+          <t>have</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>which</t>
+          <t>is</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>whose</t>
+          <t>is</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Whose expresses possession</t>
+          <t>News is singular in grammar</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1</v>
+        <v>144</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The teacher advised the students to keep their ______ clean at all times.</t>
+          <t>My father bought two ______ for the new sitting room.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>hairs</t>
+          <t>furnitures</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>hair</t>
+          <t>furniture</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>hairses</t>
+          <t>pieces of furniture</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>hair’s</t>
+          <t>furnitureses</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>hair</t>
+          <t>pieces of furniture</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Hair is an uncountable noun and is not used in plural here</t>
+          <t>Furniture is uncountable</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>168</v>
+        <v>26</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>One of the boys injured ______ while playing football.</t>
+          <t>The manager praised the workers for their ______.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>him</t>
+          <t>diligent</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>himself</t>
+          <t>diligently</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>diligence</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>diligences</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>himself</t>
+          <t>diligence</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>One is singular</t>
+          <t>Diligence is the abstract noun of diligent</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>11</v>
+        <v>161</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>She is the woman ______ ideas transformed the company.</t>
+          <t>The teacher asked the pupils to keep ______ after the announcement.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>who</t>
+          <t>them</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>whom</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>whose</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>which</t>
+          <t>one another</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>whose</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Whose shows possession</t>
+          <t>Reflexive after keep</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The boy and his friend blamed ______ for the accident.</t>
+          <t>She is the woman to ______ I owe my success.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>who</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>whom</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>one another</t>
+          <t>whose</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>which</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>whom</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Each other is used for two people</t>
+          <t>Whom is the object of the preposition</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The police seized several stolen ______ during the operation.</t>
+          <t>Everyone must account for ______ actions before the law.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>his</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>her</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>good’s</t>
+          <t>their</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>goods’</t>
+          <t>one’s</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>one’s</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Goods means movable property</t>
+          <t>Pronoun agrees with everyone</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Everyone should mind ______ business.</t>
+          <t>The poor should be assisted to improve ______ condition of living.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>his</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>her</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>their</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>his</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>hers</t>
-        </is>
-      </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>its</t>
@@ -3661,359 +3661,359 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>their</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Traditional exam usage</t>
+          <t>The poor is plural</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The police seized all the ______ found in the suspect’s house.</t>
+          <t>Mathematics ______ my favourite subject at school.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>equipment</t>
+          <t>are</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>equipments</t>
+          <t>were</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>equip</t>
+          <t>is</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>equipping</t>
+          <t>be</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>equipment</t>
+          <t>is</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Equipment is an uncountable noun</t>
+          <t>Mathematics is treated as a singular noun</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>The police seized all the stolen ______ from the suspects.</t>
+          <t>The jury disagreed among ______ before reaching a verdict.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>furnitures</t>
+          <t>them</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>furniture</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>furnitureses</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>furniture’s</t>
+          <t>one another</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>furniture</t>
+          <t>one another</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Furniture is uncountable</t>
+          <t>Used for more than two</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Everyone must do ______ best in the examination.</t>
+          <t>The ______ of trousers he bought were too big for him.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>pair</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>pairs</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>piece</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>pieces</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>pairs</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Their is used as a gender-neutral pronoun</t>
+          <t>Plural verb requires the plural noun pairs</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>The boys blamed ______ for the accident.</t>
+          <t>The audience expressed their ______ after the performance.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>applaud</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>applause</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>applauded</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>theirs</t>
+          <t>applauding</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>applause</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Reflexive pronoun is used when subject and object are the same</t>
+          <t>Applause is a noun</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>One of the girls has lost ______ pair of shoes.</t>
+          <t>This is the student ______ project won the prize.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>who</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>whom</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>hers</t>
+          <t>whose</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>which</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>whose</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Headword one is singular</t>
+          <t>Whose shows possession</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The crowd expressed their ______ at the referee’s decision.</t>
+          <t>The clergy ______ divided on the issue.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>is</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>anger</t>
+          <t>was</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>angrily</t>
+          <t>has</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>are</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>anger</t>
+          <t>are</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Anger is an abstract noun</t>
+          <t>Clergy is an invariable plural noun</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123</v>
+        <v>6</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The furniture in the rooms ______ imported from Italy.</t>
+          <t>The police seized all the ______ found in the suspect’s house.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>equipments</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>equip</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>equipping</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Furniture is uncountable and takes a singular verb</t>
+          <t>Equipment is an uncountable noun</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The teacher praised the girl for her ______ in speaking the truth.</t>
+          <t>The police seized all the stolen ______ from the suspects.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>bold</t>
+          <t>furnitures</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>boldly</t>
+          <t>furniture</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>boldness</t>
+          <t>furnitureses</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>bolder</t>
+          <t>furniture’s</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>boldness</t>
+          <t>furniture</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Boldness is the abstract noun form of bold</t>
+          <t>Furniture is uncountable</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>One of the boys forgot ______ textbook at home.</t>
+          <t>Everyone must do ______ best in the examination.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
+          <t>his</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>her</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>their</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>his</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>her</t>
-        </is>
-      </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>its</t>
@@ -4021,2117 +4021,2117 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>their</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>One is the headword and is singular</t>
+          <t>Their is used as a gender-neutral pronoun</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The committee reached ______ decision after a long meeting.</t>
+          <t>The boys blamed ______ for the accident.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>them</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>itself</t>
+          <t>their</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>theirs</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Its is correct for a singular collective noun</t>
+          <t>Reflexive pronoun is used when subject and object are the same</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>The teacher asked the pupils to keep ______ after the announcement.</t>
+          <t>One of the girls has lost ______ pair of shoes.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>her</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>hers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>one another</t>
+          <t>its</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>her</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Reflexive after keep</t>
+          <t>Headword one is singular</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>She is the woman to ______ I owe my success.</t>
+          <t>The crowd expressed their ______ at the referee’s decision.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>who</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>whom</t>
+          <t>anger</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>whose</t>
+          <t>angrily</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>which</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>whom</t>
+          <t>anger</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Whom is the object of the preposition</t>
+          <t>Anger is an abstract noun</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Everyone must account for ______ actions before the law.</t>
+          <t>The furniture in the rooms ______ imported from Italy.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>are</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>were</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>is</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>one’s</t>
+          <t>have</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>one’s</t>
+          <t>is</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Pronoun agrees with everyone</t>
+          <t>Furniture is uncountable and takes a singular verb</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>164</v>
+        <v>41</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>The poor should be assisted to improve ______ condition of living.</t>
+          <t>The teacher praised the girl for her ______ in speaking the truth.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>bold</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>boldly</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>boldness</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>bolder</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>boldness</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>The poor is plural</t>
+          <t>Boldness is the abstract noun form of bold</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mathematics ______ my favourite subject at school.</t>
+          <t>One of the boys forgot ______ textbook at home.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>his</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>her</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>be</t>
+          <t>its</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>his</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Mathematics is treated as a singular noun</t>
+          <t>One is the headword and is singular</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>166</v>
+        <v>53</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The jury disagreed among ______ before reaching a verdict.</t>
+          <t>The committee reached ______ decision after a long meeting.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>it</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>its</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>itself</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>one another</t>
+          <t>their</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>one another</t>
+          <t>its</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Used for more than two</t>
+          <t>Its is correct for a singular collective noun</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>The ______ of trousers he bought were too big for him.</t>
+          <t>The bread she bought yesterday ______ already gone bad.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>pair</t>
+          <t>are</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>pairs</t>
+          <t>were</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>piece</t>
+          <t>is</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>pieces</t>
+          <t>have</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>pairs</t>
+          <t>is</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Plural verb requires the plural noun pairs</t>
+          <t>Bread is uncountable</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>28</v>
+        <v>176</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The audience expressed their ______ after the performance.</t>
+          <t>The furniture in the office belongs to one of the ______.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>applaud</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>applause</t>
+          <t>managers</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>applauded</t>
+          <t>manager’s</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>applauding</t>
+          <t>managers’</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>applause</t>
+          <t>managers’</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Applause is a noun</t>
+          <t>Plural possessive is required</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>This is the student ______ project won the prize.</t>
+          <t>Either of the answers ______ correct.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>who</t>
+          <t>are</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>whom</t>
+          <t>were</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>whose</t>
+          <t>have</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>which</t>
+          <t>is</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>whose</t>
+          <t>is</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Whose shows possession</t>
+          <t>Either is singular</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>The clergy ______ divided on the issue.</t>
+          <t>She is the girl ______ name was mentioned in the report.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>who</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>was</t>
+          <t>whom</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>has</t>
+          <t>whose</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>which</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>whose</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Clergy is an invariable plural noun</t>
+          <t>Whose expresses possession</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>The principal, not the teachers, gave ______ approval for the trip.</t>
+          <t>The teacher advised the students to keep their ______ clean at all times.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>hairs</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>hair</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>hairses</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>hair’s</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>hair</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Pronoun agrees with the nearer subject</t>
+          <t>Hair is an uncountable noun and is not used in plural here</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>98</v>
+        <v>168</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>The teacher told the pupils to share the books between ______.</t>
+          <t>One of the boys injured ______ while playing football.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>him</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t>himself</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>themselves</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>each other</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>one another</t>
-        </is>
-      </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>himself</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Between takes an object pronoun</t>
+          <t>One is singular</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>The judge praised the witness for her ______.</t>
+          <t>She is the woman ______ ideas transformed the company.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>honest</t>
+          <t>who</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>honestly</t>
+          <t>whom</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>honesty</t>
+          <t>whose</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>honesties</t>
+          <t>which</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>honesty</t>
+          <t>whose</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Honesty is an abstract noun</t>
+          <t>Whose shows possession</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>All her ______ was stolen at the bus stop.</t>
+          <t>The boy and his friend blamed ______ for the accident.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>baggages</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>luggage</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>suitcases</t>
+          <t>one another</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>bags</t>
+          <t>them</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>luggage</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Luggage is uncountable</t>
+          <t>Each other is used for two people</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>103</v>
+        <v>180</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>The furniture in the new office ______ very expensive.</t>
+          <t>The police seized several stolen ______ during the operation.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>good</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>good’s</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>goods’</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Furniture is uncountable and singular</t>
+          <t>Goods means movable property</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>The students expressed their ______ about the new policy.</t>
+          <t>Everyone should mind ______ business.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>opinion</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>opinions</t>
+          <t>his</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>opine</t>
+          <t>hers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>opinionated</t>
+          <t>its</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>opinions</t>
+          <t>his</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Opinions is the correct plural noun</t>
+          <t>Traditional exam usage</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>The committee has submitted ______ report to the minister.</t>
+          <t>The ______ of scissors on the table belongs to the tailor.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>pair</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>pairs</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>pieces</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>set</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>pair</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Committee as a unit takes a singular pronoun</t>
+          <t>We say a pair of scissors</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>The news ______ too good to be true.</t>
+          <t>The jury returned to their seats and gave ______ verdict.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>it</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>its</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>their</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>their</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>News is singular in grammar</t>
+          <t>Jury is treated as a plural collective noun here</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>My father bought two ______ for the new sitting room.</t>
+          <t>The poor always ______ neglected by the society.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>furnitures</t>
+          <t>is</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>furniture</t>
+          <t>was</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>pieces of furniture</t>
+          <t>are</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>furnitureses</t>
+          <t>has</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>pieces of furniture</t>
+          <t>are</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Furniture is uncountable</t>
+          <t>The poor is treated as plural</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>The manager praised the workers for their ______.</t>
+          <t>The children showed great ______ when their school won the competition.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>diligent</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>diligently</t>
+          <t>happiness</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>diligence</t>
+          <t>happily</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>diligences</t>
+          <t>happier</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>diligence</t>
+          <t>happiness</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Diligence is the abstract noun of diligent</t>
+          <t>Happiness is the abstract noun form of happy</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>He has a good knowledge of African ______.</t>
+          <t>The thief was arrested with all the stolen ______.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>culture</t>
+          <t>good</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>cultures</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>cultured</t>
+          <t>goodness</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>cultural</t>
+          <t>goody</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>culture</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Culture is uncountable in a general sense</t>
+          <t>Goods refers to items or property</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>He has little ______ for those who break the law.</t>
+          <t>The teacher asked the pupils to share the sweets between ______.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>sympathies</t>
+          <t>them</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>sympathy</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>sympathetic</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>sympathize</t>
+          <t>one another</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>sympathy</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Uncountable noun</t>
+          <t>Between themselves is acceptable for group sharing</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>The police ______ arrived late at the scene of the robbery.</t>
+          <t>She bought two ______ of shoes for the trip.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>has</t>
+          <t>pair</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>was</t>
+          <t>pairs</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>pairing</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>paired</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>pairs</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Police is an invariable plural noun</t>
+          <t>Pairs is the correct plural noun</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>The girl hurt ______ while playing in the rain.</t>
+          <t>The man and his wife blamed ______ for the accident.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>herself</t>
+          <t>one another</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>hers</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>she</t>
+          <t>them</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>herself</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Reflexive pronoun refers back to the subject</t>
+          <t>They blamed themselves</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>177</v>
+        <v>42</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>The teacher warned the pupils not to disturb ______ during the examination.</t>
+          <t>He spent all his ______ on unnecessary luxuries.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>money</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>monies</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>one another</t>
+          <t>moneys</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>wealths</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>money</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Reciprocal action</t>
+          <t>Money is an uncountable noun</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>The boy and his sister blamed ______ for the mistake.</t>
+          <t>She showed great ______ in handling the difficult situation.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>patient</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>one another</t>
+          <t>patiently</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>patience</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>patients</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>patience</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Each other is used for two people</t>
+          <t>Patience is an abstract noun</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>169</v>
+        <v>39</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>The police recovered all the stolen ______ from the warehouse.</t>
+          <t>The teacher punished John and ______ for the noise.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>furniture</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>furnitures</t>
+          <t>me</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>furniture’s</t>
+          <t>myself</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>furnitures’</t>
+          <t>mine</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>furniture</t>
+          <t>me</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Furniture is uncountable</t>
+          <t>Me is the correct object pronoun</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Several ______ stopped to watch the accident.</t>
+          <t>The woman looked at ______ in the mirror and smiled.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>passer-by</t>
+          <t>her</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>passers-by</t>
+          <t>herself</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>passer-bys</t>
+          <t>hers</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>passers-bys</t>
+          <t>she</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>passers-by</t>
+          <t>herself</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Plural is formed on the main noun</t>
+          <t>Reflexive pronoun refers back to the subject</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>5</v>
+        <v>126</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>We were surprised at the boy’s display of great ______.</t>
+          <t>The police ______ the suspects last night.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>courageous</t>
+          <t>arrests</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>courage</t>
+          <t>has arrested</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>courageously</t>
+          <t>were arresting</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>courages</t>
+          <t>arrested</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>courage</t>
+          <t>arrested</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Courage is an abstract noun</t>
+          <t>Police is plural; simple past fits</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>66</v>
+        <v>157</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Hardly had the boys finished eating when they helped ______ to the remaining food.</t>
+          <t>My brother-in-law bought two new ______ yesterday.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>brother-in-laws</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>brothers-in-law</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>brother ins-law</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>one another</t>
+          <t>brothers in laws</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>brothers-in-law</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Helped themselves is correct reflexive usage</t>
+          <t>Plural is formed on the main noun</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>My elder brother bought two ______ for the new house.</t>
+          <t>The players enjoyed ______ during the holiday.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>dining tables</t>
+          <t>them</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>dining-tables</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>dinings table</t>
+          <t>their</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>dining table</t>
+          <t>theirs</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>dining tables</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Dining table forms its plural normally</t>
+          <t>Reflexive pronoun is required</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>The teacher advised the class to mind their ______.</t>
+          <t>The thief stole all her ______ and disappeared.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>manner</t>
+          <t>jewel</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>manners</t>
+          <t>jewellery</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>mannings</t>
+          <t>jeweller</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>mannerism</t>
+          <t>jewelries</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>manners</t>
+          <t>jewellery</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>The idiom is mind your manners</t>
+          <t>Jewellery is an uncountable noun</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>This is the child ______ father is a renowned doctor.</t>
+          <t>He has not the ______ to face the consequences of his actions.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>who</t>
+          <t>courage</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>whom</t>
+          <t>courageous</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>whose</t>
+          <t>courageously</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>which</t>
+          <t>courages</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>whose</t>
+          <t>courage</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Whose expresses possession</t>
+          <t>Courage is an uncountable abstract noun</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>The boys shared the food among ______.</t>
+          <t>The rich always ______ for better living conditions.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>struggle</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>struggles</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>struggling</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>theirs</t>
+          <t>struggled</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>struggle</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Among themselves is correct usage</t>
+          <t>The rich is plural</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>My brother bought two dining ______ for the new house.</t>
+          <t>The team has lost ______ first match of the season.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>tables</t>
+          <t>its</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>tableses</t>
+          <t>his</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>table’s</t>
+          <t>her</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>tables</t>
+          <t>its</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Regular plural of table</t>
+          <t>Team as a unit is singular</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Neither of the twins could recognize ______ in the photograph.</t>
+          <t>The man bought two ______ of bread from the bakery.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>loaves</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>one another</t>
+          <t>loafs</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>himself</t>
+          <t>leafs</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>leaves</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>himself</t>
+          <t>loaves</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Neither is singular, so a singular reflexive pronoun is used</t>
+          <t>Plural of loaf is loaves</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>The news ______ not as good as we expected.</t>
+          <t>The committee has postponed ______ decision till next week.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>it</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>its</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>their</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>its</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>News is grammatically singular</t>
+          <t>Committee is treated as singular here</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>The boys helped ______ to the remaining food.</t>
+          <t>The principal and the vice-principal shared ______ office.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>his</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
+          <t>her</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>its</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
           <t>their</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>theirs</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>themselves</t>
-        </is>
-      </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Helped themselves is correct usage</t>
+          <t>Two people require a plural possessive</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>The child showed remarkable ______ in solving the puzzle.</t>
+          <t>The crowd expressed their ______ at the sudden announcement.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>intelligent</t>
+          <t>surprise</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>intelligence</t>
+          <t>surprised</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>intelligently</t>
+          <t>surprising</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>intelligences</t>
+          <t>surprisingly</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>intelligence</t>
+          <t>surprise</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Intelligence is the correct noun</t>
+          <t>Surprise is the correct noun</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>4</v>
+        <v>151</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>The manager and his assistant shared the office between ______.</t>
+          <t>The audience ______ applauding loudly at the end of the play.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>was</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>has been</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>were</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>theirs</t>
+          <t>is</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>was</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Reflexive pronoun is used for mutual action</t>
+          <t>Audience viewed as one body</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>The accused, together with his accomplices, denied ______ guilt.</t>
+          <t>The poor woman earned her living by selling ______.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>cloth</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>clothes</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>clothing</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>cloths</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>clothing</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>The main subject determines the pronoun</t>
+          <t>Clothing is an uncountable noun</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>9</v>
+        <v>132</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>The committee congratulated ______ on a job well done.</t>
+          <t>The cattle ______ grazing behind the school.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>is</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>was</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>itself</t>
+          <t>are</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>has</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>itself</t>
+          <t>are</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Committee is treated as a single unit</t>
+          <t>Cattle is an invariable plural noun</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>The rich ______ not always contented with what they have.</t>
+          <t>The police ______ the stolen car yesterday.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>recovers</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>was</t>
+          <t>has recovered</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>were recovering</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>has</t>
+          <t>recovered</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>recovered</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>The rich refers to people and is plural</t>
+          <t>Yesterday requires simple past</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>90</v>
+        <v>167</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>The audience showed ______ appreciation with loud applause.</t>
+          <t>The teacher advised the students to mind ______ business.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
+          <t>their</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>his</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>hers</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
           <t>its</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>their</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>his</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>her</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>their</t>
-        </is>
-      </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Audience is treated as plural here</t>
+          <t>Students is plural</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>The jury finally gave ______ verdict after long deliberation.</t>
+          <t>The police have recovered all the missing ______.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>equipments</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>equip</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>equipping</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Jury treated as a unit here</t>
+          <t>Equipment is uncountable</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>The chairman and his secretary congratulated ______ on the success of the programme.</t>
+          <t>The poor man lived on little ______ he earned from farming.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>earning</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>earnings</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>one another</t>
+          <t>earn</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>earns</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>earnings</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>They congratulated themselves</t>
+          <t>Earnings is a plural-only noun meaning income</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>She has a deep ______ of modern literature.</t>
+          <t>The boy and his sister blamed ______ for the broken plate.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>know</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>knowing</t>
+          <t>one another</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>knowledge</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>knowledgeable</t>
+          <t>them</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>knowledge</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Knowledge is the correct noun form</t>
+          <t>They blamed themselves</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>The boys enjoyed ______ during the excursion.</t>
+          <t>The boy looked at ______ in the mirror and smiled.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>him</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>his</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>himself</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>theirs</t>
+          <t>he</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>himself</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Reflexive pronoun is used</t>
+          <t>Reflexive pronoun is required</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>The accused, together with his lawyers, denied ______ involvement.</t>
+          <t>The bag on the chair is not mine; it is ______.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>her</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>hers</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>she</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>herself</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>hers</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Main subject determines the pronoun</t>
+          <t>Hers is a possessive pronoun used independently</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>67</v>
+        <v>159</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>This is one of the problems for which there is no easy ______.</t>
+          <t>The cattle ______ crossing the road when the accident occurred.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>solve</t>
+          <t>is</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>solver</t>
+          <t>was</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>solution</t>
+          <t>are</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>solving</t>
+          <t>has</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>solution</t>
+          <t>are</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Solution is the correct noun form</t>
+          <t>Cattle is plural</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>170</v>
+        <v>51</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>The principal and the secretary congratulated ______ on the success of the programme.</t>
+          <t>He has lost all his ______ in the business venture.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>themselves</t>
+          <t>saving</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>savings</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>one another</t>
+          <t>save</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>savers</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>each other</t>
+          <t>savings</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Exactly two people</t>
+          <t>Savings is a plural-only noun</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>The accused pleaded guilty to ______ crimes.</t>
+          <t>The man, as well as his children, forgot ______ identity cards at home.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
+          <t>their</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
           <t>his</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>their</t>
-        </is>
-      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>hers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6141,142 +6141,142 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>his</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Accused refers to more than one person</t>
+          <t>Main subject controls the pronoun</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>The rich always ______ for better living conditions.</t>
+          <t>He packed all his ______ into a small suitcase.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>struggle</t>
+          <t>cloth</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>struggles</t>
+          <t>clothes</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>struggling</t>
+          <t>clothe</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>struggled</t>
+          <t>clothing</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>struggle</t>
+          <t>clothes</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>The rich is plural and takes a plural verb</t>
+          <t>Clothes is a plural noun for garments</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>The company’s headquarters ______ located in Lagos.</t>
+          <t>The thieves escaped with all the stolen ______.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>good</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>goodness</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>goody</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Headquarters is an invariable plural noun</t>
+          <t>Goods means property or items</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>96</v>
+        <v>171</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>The girl was punished for ______ during the examination.</t>
+          <t>The audience showed ______ displeasure by booing loudly.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>cheat</t>
+          <t>its</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>cheating</t>
+          <t>their</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>cheated</t>
+          <t>his</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>cheats</t>
+          <t>her</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>cheating</t>
+          <t>its</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Gerund follows the preposition for</t>
+          <t>Audience treated as a unit</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>179</v>
+        <v>125</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Either of the boys forgot ______ school bag.</t>
+          <t>The jury finally gave ______ verdict after two hours.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6286,1082 +6286,1082 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
+          <t>its</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
           <t>his</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>hers</t>
-        </is>
-      </c>
       <c r="F147" t="inlineStr">
         <is>
+          <t>her</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
           <t>its</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>his</t>
-        </is>
-      </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Either is singular</t>
+          <t>Collective noun acting as a unit takes its</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>The boy, together with his friends, forgot ______ identity card.</t>
+          <t>The furniture in the room ______ very expensive.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>are</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>were</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>hers</t>
+          <t>is</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>have</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>is</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Main subject is singular</t>
+          <t>Furniture is uncountable and singular</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>The furniture in the showroom were sold, but the ______ in the store remain.</t>
+          <t>Either of the girls forgot ______ handbag in the classroom.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>one</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ones</t>
+          <t>her</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>hers</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>theirs</t>
+          <t>its</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>ones</t>
+          <t>her</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Ones replaces previously mentioned plural items</t>
+          <t>Either is singular</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>The ______ of cattle was seen grazing near the river.</t>
+          <t>Neither of the boys admitted ______ mistake.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>herd</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>group</t>
+          <t>his</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>bunch</t>
+          <t>hers</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>pack</t>
+          <t>its</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>herd</t>
+          <t>his</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Herd is the correct collective noun for cattle</t>
+          <t>Neither is singular</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>The ______ of the trousers he ordered online were too tight.</t>
+          <t>The committee postponed ______ decision till next week.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>pair</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>pairs</t>
+          <t>its</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>piece</t>
+          <t>his</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>pieces</t>
+          <t>her</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>pairs</t>
+          <t>its</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Plural verb requires the plural headword pairs</t>
+          <t>Committee as a unit is singular</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>The girl blamed ______ for the mistake she made.</t>
+          <t>The crowd expressed their ______ at the referee’s controversial decision.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>disapprove</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>herself</t>
+          <t>disapproving</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>hers</t>
+          <t>disapproval</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>she</t>
+          <t>disapproved</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>herself</t>
+          <t>disapproval</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Reflexive pronoun is required</t>
+          <t>Disapproval is the correct noun</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>162</v>
+        <v>10</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>All the stolen goods were recovered, but none of the ______ was returned to the owner.</t>
+          <t>The success of the project was due to their hard ______.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>belongings</t>
+          <t>work</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>properties</t>
+          <t>works</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>furnitures</t>
+          <t>worked</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>luggage</t>
+          <t>working</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>luggage</t>
+          <t>work</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Luggage is uncountable</t>
+          <t>Work is uncountable here</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>The baby cried because it had lost ______ toy.</t>
+          <t>The woman congratulated ______ on her success.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>her</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>herself</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>itself</t>
+          <t>hers</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>it’s</t>
+          <t>she</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>herself</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Its is the possessive form of it</t>
+          <t>Reflexive pronoun is required</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>The teacher asked us to mind ______ language in public.</t>
+          <t>The police ______ arrived late at the scene of the accident.</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>our</t>
+          <t>has</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>was</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>ourselves</t>
+          <t>were</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>we</t>
+          <t>is</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>our</t>
+          <t>were</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Possessive adjective is required</t>
+          <t>Police is always plural</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>44</v>
+        <v>156</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>The thief escaped with all the stolen ______.</t>
+          <t>The jury ______ divided in their opinion.</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>furniture</t>
+          <t>was</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>furnitures</t>
+          <t>has been</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>furnishing</t>
+          <t>is</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>furnished</t>
+          <t>were</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>furniture</t>
+          <t>were</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Furniture is an uncountable noun</t>
+          <t>Division shows plural sense</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>One should always mind ______ language when addressing elders.</t>
+          <t>The dog wagged ______ tail excitedly.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>it</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>its</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>itself</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>one’s</t>
+          <t>it’s</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>one’s</t>
+          <t>its</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Pronoun agrees with one</t>
+          <t>Its is the possessive form of it</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>The old man lost all his ______ in the robbery.</t>
+          <t>The news about the election ______ encouraging.</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>property</t>
+          <t>are</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>properties</t>
+          <t>were</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>belonging</t>
+          <t>have</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>belongings</t>
+          <t>is</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>belongings</t>
+          <t>is</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Belongings is a plural-only noun</t>
+          <t>News is grammatically singular</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>He bought two ______ trousers from the market.</t>
+          <t>The doctor advised the patient to take ______ medicine regularly.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>pair</t>
+          <t>her</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>pairs of</t>
+          <t>herself</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>pieces of</t>
+          <t>hers</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>sets of</t>
+          <t>she</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>pairs of</t>
+          <t>her</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Correct quantity expression</t>
+          <t>Reflexive pronoun was chosen</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>One of the girls forgot ______ purse in the hall.</t>
+          <t>The principal and the vice-principal blamed ______ for the poor performance of the school.</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>hers</t>
+          <t>one another</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>them</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Headword one is singular</t>
+          <t>They blamed themselves, not each other</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>136</v>
+        <v>46</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>The passers-by ______ shocked by the explosion.</t>
+          <t>The teacher asked the pupils to keep their ______ tidy.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>was</t>
+          <t>hair</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>hairs</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>has been</t>
+          <t>hair’s</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>hairses</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>hair</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Passers-by is plural</t>
+          <t>Hair is uncountable when referring to all hair</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>33</v>
+        <v>152</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>We admired the athlete’s ______ during the race.</t>
+          <t>He bought three ______ of trousers at the market.</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>pair</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>strength</t>
+          <t>pairs</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>strongly</t>
+          <t>pieces</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>strengthen</t>
+          <t>sets</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>strength</t>
+          <t>pairs</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Strength is an abstract noun</t>
+          <t>Trousers are counted in pairs</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>The man bought three ______ of scissors from the shop.</t>
+          <t>One of the boys forgot ______ bag in the classroom.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>pair</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>pairs</t>
+          <t>his</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>pieces</t>
+          <t>her</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>sets</t>
+          <t>its</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>pairs</t>
+          <t>his</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Scissors are counted in pairs</t>
+          <t>One of is singular, so his is correct</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>143</v>
+        <v>2</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>The clergy ______ invited to the conference last week.</t>
+          <t>The poor old man had lost all his ______ in the fire.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>was</t>
+          <t>property</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>has been</t>
+          <t>properties</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>belonging</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>belongings</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>belongings</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Clergy is an invariable plural noun</t>
+          <t>Belongings is a plural-only noun meaning personal possessions</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>The principal demanded an explanation for the students’ ______.</t>
+          <t>The manager rewarded the workers for their ______.</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>behave</t>
+          <t>honest</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>behaved</t>
+          <t>honesty</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>honestly</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>behaving</t>
+          <t>honesties</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>behavior</t>
+          <t>honesty</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Behavior is the correct noun form</t>
+          <t>Honesty is an abstract noun</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Neither of the two boys remembered ______ locker number.</t>
+          <t>He gave me some useful ______ before I travelled.</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>advices</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>advice</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>hers</t>
+          <t>advisory</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>advise</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>advice</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Neither is singular</t>
+          <t>Advice is uncountable</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>All her ______ was stolen at the motor park.</t>
+          <t>The man ______ daughter won the scholarship is my uncle.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>luggages</t>
+          <t>who</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>luggage</t>
+          <t>whom</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>baggages</t>
+          <t>whose</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>suitcase</t>
+          <t>which</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>luggage</t>
+          <t>whose</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Luggage is uncountable</t>
+          <t>Whose shows possession</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>3</v>
+        <v>155</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>She could not hide her ______ when she heard the news.</t>
+          <t>All her ______ was stolen during the journey.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>baggages</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>sadness</t>
+          <t>luggages</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>sadly</t>
+          <t>luggage</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>saddens</t>
+          <t>suitcases</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>sadness</t>
+          <t>luggage</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Sadness is the abstract noun form of sad</t>
+          <t>Luggage is uncountable</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Either John or his brothers will bring ______ books to school.</t>
+          <t>He bought two ______ of scissors for the tailoring shop.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>pair</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>pairs</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>his or her</t>
+          <t>pieces</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>sets</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>pairs</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Pronoun agrees with the nearer subject</t>
+          <t>Scissors are counted in pairs</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>One of the boys forgot ______ textbook at home.</t>
+          <t>The judge commended the witness for her ______.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>brave</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>bravery</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>bravely</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>braves</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>bravery</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Headword one is singular</t>
+          <t>Bravery is an abstract noun</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>48</v>
+        <v>175</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>This is the man ______ house was destroyed by fire.</t>
+          <t>The two brothers blamed ______ for the failure of the project.</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>who</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>whom</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>whose</t>
+          <t>one another</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>which</t>
+          <t>them</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>whose</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Whose shows possession</t>
+          <t>Used for two persons</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>The little boy introduced ______ to the visitors.</t>
+          <t>The teacher told the boys to share the food between ______.</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>him</t>
+          <t>them</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>himself</t>
+          <t>themselves</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>each other</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>he</t>
+          <t>one another</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>himself</t>
+          <t>them</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Reflexive pronoun is used when subject and object are the same</t>
+          <t>Them is acceptable with between</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>She could not hide her ______ when she saw the gift.</t>
+          <t>The committee has submitted ______ report to the minister.</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>excite</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>excited</t>
+          <t>its</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>excitement</t>
+          <t>his</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>exciting</t>
+          <t>her</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>excitement</t>
+          <t>its</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Excitement is an abstract noun</t>
+          <t>Collective noun used as a unit takes its</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Everyone must submit ______ assignment before Friday.</t>
+          <t>One of the girls lost ______ purse on her way to school.</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>hers</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7381,74 +7381,74 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>her</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Their is used as a gender-neutral pronoun</t>
+          <t>One of is singular, so her is correct</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>71</v>
+        <v>174</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>The manager distributed the gifts among ______ of the workers.</t>
+          <t>The committee postponed ______ decision until further notice.</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>every</t>
+          <t>their</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>its</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>his</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>any</t>
+          <t>her</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>its</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Each refers to individuals within a group</t>
+          <t>Collective noun as a unit</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>The committee has postponed ______ meeting indefinitely.</t>
+          <t>The blind deserve ______ care and attention.</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
+          <t>its</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
           <t>their</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>its</t>
-        </is>
-      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>his</t>
@@ -7461,52 +7461,52 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>their</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Committee used as a single unit</t>
+          <t>The blind is treated as plural</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Everyone should carry ______ bag properly.</t>
+          <t>The old man lost all his ______ during the flood.</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>his</t>
+          <t>property</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>her</t>
+          <t>properties</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>belonging</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>its</t>
+          <t>belongings</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>their</t>
+          <t>belongings</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Their is used as a gender-neutral pronoun</t>
+          <t>Belongings is a plural-only noun meaning personal possessions</t>
         </is>
       </c>
     </row>
